--- a/light_fight/Assets/Excels/StatConfig.xlsx
+++ b/light_fight/Assets/Excels/StatConfig.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="infos" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="stats" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,16 +22,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">id</t>
+    <t xml:space="preserve">ID</t>
   </si>
   <si>
-    <t xml:space="preserve">type</t>
+    <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Value</t>
   </si>
   <si>
-    <t xml:space="preserve">modifier</t>
+    <t xml:space="preserve">Modifier</t>
   </si>
   <si>
     <t xml:space="preserve">Attack</t>
@@ -59,7 +59,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,6 +83,21 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial Black"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,18 +106,12 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF81D41A"/>
-        <bgColor rgb="FF969696"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -139,28 +148,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -226,7 +243,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF81D41A"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -422,544 +439,533 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15.36"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="3" width="11.54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="2" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="2" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="2" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
+      <c r="A65" s="2"/>
+      <c r="B65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
+      <c r="A67" s="2"/>
+      <c r="B67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
+      <c r="A71" s="2"/>
+      <c r="B71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
+      <c r="A72" s="2"/>
+      <c r="B72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-    </row>
-    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C51:F419 E1:F50">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
